--- a/filer/35478205_geia.xlsx
+++ b/filer/35478205_geia.xlsx
@@ -639,7 +639,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse B · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/35478205_geia.xlsx
+++ b/filer/35478205_geia.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -668,35 +668,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1522,35 +1522,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2808,35 +2808,35 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
@@ -3224,49 +3224,49 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B59" s="11">
         <f>'balance_raw_35478205'!$B$36</f>
         <v/>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="11">
         <f>'balance_raw_35478205'!$C$36</f>
         <v/>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="11">
         <f>'balance_raw_35478205'!$D$36</f>
         <v/>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="11">
         <f>'balance_raw_35478205'!$E$36</f>
         <v/>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="11">
         <f>'balance_raw_35478205'!$F$36</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="9">
+      <c r="H59" s="12">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="12">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="12">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="12">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="9">
+      <c r="L59" s="12">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
@@ -3274,7 +3274,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B60" s="5">
@@ -3322,7 +3322,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B61" s="8">
@@ -3370,7 +3370,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3416,49 +3416,49 @@
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B63" s="11">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B63" s="8">
         <f>'balance_raw_35478205'!$B$40</f>
         <v/>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="8">
         <f>'balance_raw_35478205'!$C$40</f>
         <v/>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="8">
         <f>'balance_raw_35478205'!$D$40</f>
         <v/>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="8">
         <f>'balance_raw_35478205'!$E$40</f>
         <v/>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="8">
         <f>'balance_raw_35478205'!$F$40</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="12">
+      <c r="H63" s="9">
         <f>IFERROR(B63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="9">
         <f>IFERROR(C63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="J63" s="12">
+      <c r="J63" s="9">
         <f>IFERROR(D63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="K63" s="12">
+      <c r="K63" s="9">
         <f>IFERROR(E63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="L63" s="12">
+      <c r="L63" s="9">
         <f>IFERROR(F63/$B$63*100,"")</f>
         <v/>
       </c>
@@ -3466,7 +3466,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3514,7 +3514,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B65" s="8">
@@ -3562,7 +3562,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3610,7 +3610,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3658,7 +3658,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3706,7 +3706,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3754,7 +3754,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3800,337 +3800,263 @@
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B71" s="8">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B71" s="11">
         <f>'balance_raw_35478205'!$B$48</f>
         <v/>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="11">
         <f>'balance_raw_35478205'!$C$48</f>
         <v/>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="11">
         <f>'balance_raw_35478205'!$D$48</f>
         <v/>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="11">
         <f>'balance_raw_35478205'!$E$48</f>
         <v/>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="11">
         <f>'balance_raw_35478205'!$F$48</f>
         <v/>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" s="9">
+      <c r="H71" s="12">
         <f>IFERROR(B71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="12">
         <f>IFERROR(C71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="12">
         <f>IFERROR(D71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="K71" s="9">
+      <c r="K71" s="12">
         <f>IFERROR(E71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="L71" s="9">
+      <c r="L71" s="12">
         <f>IFERROR(F71/$B$71*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B72" s="5">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B72" s="11">
         <f>'balance_raw_35478205'!$B$49</f>
         <v/>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="11">
         <f>'balance_raw_35478205'!$C$49</f>
         <v/>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="11">
         <f>'balance_raw_35478205'!$D$49</f>
         <v/>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="11">
         <f>'balance_raw_35478205'!$E$49</f>
         <v/>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="11">
         <f>'balance_raw_35478205'!$F$49</f>
         <v/>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="6">
+      <c r="H72" s="12">
         <f>IFERROR(B72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="I72" s="6">
+      <c r="I72" s="12">
         <f>IFERROR(C72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="J72" s="6">
+      <c r="J72" s="12">
         <f>IFERROR(D72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="12">
         <f>IFERROR(E72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="12">
         <f>IFERROR(F72/$B$72*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B73" s="8">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B73" s="11">
         <f>'balance_raw_35478205'!$B$50</f>
         <v/>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="11">
         <f>'balance_raw_35478205'!$C$50</f>
         <v/>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="11">
         <f>'balance_raw_35478205'!$D$50</f>
         <v/>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="11">
         <f>'balance_raw_35478205'!$E$50</f>
         <v/>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="11">
         <f>'balance_raw_35478205'!$F$50</f>
         <v/>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" s="9">
+      <c r="H73" s="12">
         <f>IFERROR(B73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="I73" s="9">
+      <c r="I73" s="12">
         <f>IFERROR(C73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="J73" s="9">
+      <c r="J73" s="12">
         <f>IFERROR(D73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="K73" s="9">
+      <c r="K73" s="12">
         <f>IFERROR(E73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="L73" s="9">
+      <c r="L73" s="12">
         <f>IFERROR(F73/$B$73*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B74" s="5">
-        <f>'balance_raw_35478205'!$B$51</f>
-        <v/>
-      </c>
-      <c r="C74" s="5">
-        <f>'balance_raw_35478205'!$C$51</f>
-        <v/>
-      </c>
-      <c r="D74" s="5">
-        <f>'balance_raw_35478205'!$D$51</f>
-        <v/>
-      </c>
-      <c r="E74" s="5">
-        <f>'balance_raw_35478205'!$E$51</f>
-        <v/>
-      </c>
-      <c r="F74" s="5">
-        <f>'balance_raw_35478205'!$F$51</f>
-        <v/>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" s="6">
-        <f>IFERROR(B74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="I74" s="6">
-        <f>IFERROR(C74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="6">
-        <f>IFERROR(D74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="K74" s="6">
-        <f>IFERROR(E74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="L74" s="6">
-        <f>IFERROR(F74/$B$74*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B75" s="11">
-        <f>'balance_raw_35478205'!$B$52</f>
-        <v/>
-      </c>
-      <c r="C75" s="11">
-        <f>'balance_raw_35478205'!$C$52</f>
-        <v/>
-      </c>
-      <c r="D75" s="11">
-        <f>'balance_raw_35478205'!$D$52</f>
-        <v/>
-      </c>
-      <c r="E75" s="11">
-        <f>'balance_raw_35478205'!$E$52</f>
-        <v/>
-      </c>
-      <c r="F75" s="11">
-        <f>'balance_raw_35478205'!$F$52</f>
-        <v/>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="12">
-        <f>IFERROR(B75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="I75" s="12">
-        <f>IFERROR(C75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="12">
-        <f>IFERROR(D75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="K75" s="12">
-        <f>IFERROR(E75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="L75" s="12">
-        <f>IFERROR(F75/$B$75*100,"")</f>
-        <v/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NØGLEOPLYSNINGER</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B76" s="11">
-        <f>'balance_raw_35478205'!$B$53</f>
-        <v/>
-      </c>
-      <c r="C76" s="11">
-        <f>'balance_raw_35478205'!$C$53</f>
-        <v/>
-      </c>
-      <c r="D76" s="11">
-        <f>'balance_raw_35478205'!$D$53</f>
-        <v/>
-      </c>
-      <c r="E76" s="11">
-        <f>'balance_raw_35478205'!$E$53</f>
-        <v/>
-      </c>
-      <c r="F76" s="11">
-        <f>'balance_raw_35478205'!$F$53</f>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B76" s="5">
+        <f>'res_raw_35478205'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C76" s="5">
+        <f>'res_raw_35478205'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>'res_raw_35478205'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E76" s="5">
+        <f>'res_raw_35478205'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>'res_raw_35478205'!$F$19</f>
         <v/>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="12">
+      <c r="H76" s="6">
         <f>IFERROR(B76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="I76" s="12">
+      <c r="I76" s="6">
         <f>IFERROR(C76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="J76" s="12">
+      <c r="J76" s="6">
         <f>IFERROR(D76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="K76" s="12">
+      <c r="K76" s="6">
         <f>IFERROR(E76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="L76" s="12">
+      <c r="L76" s="6">
         <f>IFERROR(F76/$B$76*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B77" s="11">
-        <f>'balance_raw_35478205'!$B$54</f>
-        <v/>
-      </c>
-      <c r="C77" s="11">
-        <f>'balance_raw_35478205'!$C$54</f>
-        <v/>
-      </c>
-      <c r="D77" s="11">
-        <f>'balance_raw_35478205'!$D$54</f>
-        <v/>
-      </c>
-      <c r="E77" s="11">
-        <f>'balance_raw_35478205'!$E$54</f>
-        <v/>
-      </c>
-      <c r="F77" s="11">
-        <f>'balance_raw_35478205'!$F$54</f>
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>'res_raw_35478205'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C77" s="8">
+        <f>'res_raw_35478205'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D77" s="8">
+        <f>'res_raw_35478205'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E77" s="8">
+        <f>'res_raw_35478205'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F77" s="8">
+        <f>'res_raw_35478205'!$F$20</f>
         <v/>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="12">
+      <c r="H77" s="9">
         <f>IFERROR(B77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="I77" s="12">
+      <c r="I77" s="9">
         <f>IFERROR(C77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="J77" s="12">
+      <c r="J77" s="9">
         <f>IFERROR(D77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="K77" s="12">
+      <c r="K77" s="9">
         <f>IFERROR(E77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="L77" s="12">
+      <c r="L77" s="9">
         <f>IFERROR(F77/$B$77*100,"")</f>
         <v/>
       </c>
@@ -4138,438 +4064,327 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>NØGLEOPLYSNINGER</t>
+          <t>NØGLETAL</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B80" s="5">
-        <f>'res_raw_35478205'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C80" s="5">
-        <f>'res_raw_35478205'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D80" s="5">
-        <f>'res_raw_35478205'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E80" s="5">
-        <f>'res_raw_35478205'!$E$19</f>
-        <v/>
-      </c>
-      <c r="F80" s="5">
-        <f>'res_raw_35478205'!$F$19</f>
-        <v/>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" s="6">
-        <f>IFERROR(B80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="I80" s="6">
-        <f>IFERROR(C80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="J80" s="6">
-        <f>IFERROR(D80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="K80" s="6">
-        <f>IFERROR(E80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="L80" s="6">
-        <f>IFERROR(F80/$B$80*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B81" s="8">
-        <f>'res_raw_35478205'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C81" s="8">
-        <f>'res_raw_35478205'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D81" s="8">
-        <f>'res_raw_35478205'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E81" s="8">
-        <f>'res_raw_35478205'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F81" s="8">
-        <f>'res_raw_35478205'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" s="9">
-        <f>IFERROR(B81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="I81" s="9">
-        <f>IFERROR(C81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="9">
-        <f>IFERROR(D81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="K81" s="9">
-        <f>IFERROR(E81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="L81" s="9">
-        <f>IFERROR(F81/$B$81*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>2024</v>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B81" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B82" s="13">
+        <f>IFERROR($B$4/$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="13">
+        <f>IFERROR($C$4/$C$48,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="13">
+        <f>IFERROR($D$4/$D$48,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="13">
+        <f>IFERROR($E$4/$E$48,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="13">
+        <f>IFERROR($F$4/$F$48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B83" s="14">
+        <f>IFERROR($B$18/$B$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="14">
+        <f>IFERROR($C$18/$C$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IFERROR($D$18/$D$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IFERROR($E$18/$E$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="14">
+        <f>IFERROR($F$18/$F$57*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
+          <t>Gældsrente, %</t>
         </is>
       </c>
       <c r="B84" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$48*100,"")</f>
+        <f>IFERROR($B$16/($B$73-$B$57)*100,"")</f>
         <v/>
       </c>
       <c r="C84" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$48*100,"")</f>
+        <f>IFERROR($C$16/($C$73-$C$57)*100,"")</f>
         <v/>
       </c>
       <c r="D84" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$48*100,"")</f>
+        <f>IFERROR($D$16/($D$73-$D$57)*100,"")</f>
         <v/>
       </c>
       <c r="E84" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$48*100,"")</f>
+        <f>IFERROR($E$16/($E$73-$E$57)*100,"")</f>
         <v/>
       </c>
       <c r="F84" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$48*100,"")</f>
+        <f>IFERROR($F$16/($F$73-$F$57)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
+          <t>Soliditetsgrad, %</t>
         </is>
       </c>
       <c r="B85" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <f>IFERROR($B$57/$B$48*100,"")</f>
         <v/>
       </c>
       <c r="C85" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <f>IFERROR($C$57/$C$48*100,"")</f>
         <v/>
       </c>
       <c r="D85" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <f>IFERROR($D$57/$D$48*100,"")</f>
         <v/>
       </c>
       <c r="E85" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <f>IFERROR($E$57/$E$48*100,"")</f>
         <v/>
       </c>
       <c r="F85" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <f>IFERROR($F$57/$F$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
+          <t>Gearing</t>
         </is>
       </c>
       <c r="B86" s="13">
-        <f>IFERROR($B$4/$B$48,"")</f>
+        <f>IFERROR(($B$73-$B$57)/$B$57,"")</f>
         <v/>
       </c>
       <c r="C86" s="13">
-        <f>IFERROR($C$4/$C$48,"")</f>
+        <f>IFERROR(($C$73-$C$57)/$C$57,"")</f>
         <v/>
       </c>
       <c r="D86" s="13">
-        <f>IFERROR($D$4/$D$48,"")</f>
+        <f>IFERROR(($D$73-$D$57)/$D$57,"")</f>
         <v/>
       </c>
       <c r="E86" s="13">
-        <f>IFERROR($E$4/$E$48,"")</f>
+        <f>IFERROR(($E$73-$E$57)/$E$57,"")</f>
         <v/>
       </c>
       <c r="F86" s="13">
-        <f>IFERROR($F$4/$F$48,"")</f>
+        <f>IFERROR(($F$73-$F$57)/$F$57,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
+          <t>Likviditetsgrad, %</t>
         </is>
       </c>
       <c r="B87" s="14">
-        <f>IFERROR($B$18/$B$57*100,"")</f>
+        <f>IFERROR($B$47/$B$71*100,"")</f>
         <v/>
       </c>
       <c r="C87" s="14">
-        <f>IFERROR($C$18/$C$57*100,"")</f>
+        <f>IFERROR($C$47/$C$71*100,"")</f>
         <v/>
       </c>
       <c r="D87" s="14">
-        <f>IFERROR($D$18/$D$57*100,"")</f>
+        <f>IFERROR($D$47/$D$71*100,"")</f>
         <v/>
       </c>
       <c r="E87" s="14">
-        <f>IFERROR($E$18/$E$57*100,"")</f>
+        <f>IFERROR($E$47/$E$71*100,"")</f>
         <v/>
       </c>
       <c r="F87" s="14">
-        <f>IFERROR($F$18/$F$57*100,"")</f>
+        <f>IFERROR($F$47/$F$71*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
+          <t>Rentemarginal, %</t>
         </is>
       </c>
       <c r="B88" s="13">
-        <f>IFERROR($B$16/($B$77-$B$57)*100,"")</f>
+        <f>IFERROR(B80-B84,"")</f>
         <v/>
       </c>
       <c r="C88" s="13">
-        <f>IFERROR($C$16/($C$77-$C$57)*100,"")</f>
+        <f>IFERROR(C80-C84,"")</f>
         <v/>
       </c>
       <c r="D88" s="13">
-        <f>IFERROR($D$16/($D$77-$D$57)*100,"")</f>
+        <f>IFERROR(D80-D84,"")</f>
         <v/>
       </c>
       <c r="E88" s="13">
-        <f>IFERROR($E$16/($E$77-$E$57)*100,"")</f>
+        <f>IFERROR(E80-E84,"")</f>
         <v/>
       </c>
       <c r="F88" s="13">
-        <f>IFERROR($F$16/($F$77-$F$57)*100,"")</f>
+        <f>IFERROR(F80-F84,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
+          <t>Gældsandel, %</t>
         </is>
       </c>
       <c r="B89" s="14">
-        <f>IFERROR($B$57/$B$48*100,"")</f>
+        <f>IFERROR(($B$73-$B$57)/$B$48*100,"")</f>
         <v/>
       </c>
       <c r="C89" s="14">
-        <f>IFERROR($C$57/$C$48*100,"")</f>
+        <f>IFERROR(($C$73-$C$57)/$C$48*100,"")</f>
         <v/>
       </c>
       <c r="D89" s="14">
-        <f>IFERROR($D$57/$D$48*100,"")</f>
+        <f>IFERROR(($D$73-$D$57)/$D$48*100,"")</f>
         <v/>
       </c>
       <c r="E89" s="14">
-        <f>IFERROR($E$57/$E$48*100,"")</f>
+        <f>IFERROR(($E$73-$E$57)/$E$48*100,"")</f>
         <v/>
       </c>
       <c r="F89" s="14">
-        <f>IFERROR($F$57/$F$48*100,"")</f>
+        <f>IFERROR(($F$73-$F$57)/$F$48*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
+          <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
       <c r="B90" s="13">
-        <f>IFERROR(($B$77-$B$57)/$B$57,"")</f>
+        <f>IFERROR($B$32/($B$57+$B$59)*100,"")</f>
         <v/>
       </c>
       <c r="C90" s="13">
-        <f>IFERROR(($C$77-$C$57)/$C$57,"")</f>
+        <f>IFERROR($C$32/($C$57+$C$59)*100,"")</f>
         <v/>
       </c>
       <c r="D90" s="13">
-        <f>IFERROR(($D$77-$D$57)/$D$57,"")</f>
+        <f>IFERROR($D$32/($D$57+$D$59)*100,"")</f>
         <v/>
       </c>
       <c r="E90" s="13">
-        <f>IFERROR(($E$77-$E$57)/$E$57,"")</f>
+        <f>IFERROR($E$32/($E$57+$E$59)*100,"")</f>
         <v/>
       </c>
       <c r="F90" s="13">
-        <f>IFERROR(($F$77-$F$57)/$F$57,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B91" s="14">
-        <f>IFERROR($B$47/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="14">
-        <f>IFERROR($C$47/$C$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="14">
-        <f>IFERROR($D$47/$D$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="14">
-        <f>IFERROR($E$47/$E$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="14">
-        <f>IFERROR($F$47/$F$75*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B92" s="13">
-        <f>IFERROR(B84-B88,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="13">
-        <f>IFERROR(C84-C88,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IFERROR(D84-D88,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IFERROR(E84-E88,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IFERROR(F84-F88,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B93" s="14">
-        <f>IFERROR(($B$77-$B$57)/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="C93" s="14">
-        <f>IFERROR(($C$77-$C$57)/$C$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="14">
-        <f>IFERROR(($D$77-$D$57)/$D$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="14">
-        <f>IFERROR(($E$77-$E$57)/$E$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="14">
-        <f>IFERROR(($F$77-$F$57)/$F$48*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Kapitalbindingsgrad, %</t>
-        </is>
-      </c>
-      <c r="B94" s="13">
-        <f>IFERROR($B$32/($B$57+$B$63)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="13">
-        <f>IFERROR($C$32/($C$57+$C$63)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="13">
-        <f>IFERROR($D$32/($D$57+$D$63)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>IFERROR($E$32/($E$57+$E$63)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="13">
-        <f>IFERROR($F$32/($F$57+$F$63)*100,"")</f>
-        <v/>
+        <f>IFERROR($F$32/($F$57+$F$59)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4601,19 +4416,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4671,19 +4486,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>2331</v>
+        <v>7432</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>7432</v>
+        <v>-1808</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>-1808</v>
+        <v>-1635</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-1635</v>
+        <v>2980</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>2980</v>
+        <v>-2748</v>
       </c>
     </row>
     <row r="7">
@@ -4693,19 +4508,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>3081</v>
+        <v>3090</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>3090</v>
+        <v>2923</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>2923</v>
+        <v>3042</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>3042</v>
+        <v>3374</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>3374</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="8">
@@ -4722,19 +4537,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E9" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" s="16" t="n">
         <v>66</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -4756,19 +4571,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-811</v>
+        <v>4279</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>4279</v>
+        <v>-4782</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-4782</v>
+        <v>-4743</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-4743</v>
+        <v>-446</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-446</v>
+        <v>-6831</v>
       </c>
     </row>
     <row r="12">
@@ -4778,19 +4593,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>2133</v>
+        <v>110</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>110</v>
+        <v>8369</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>8369</v>
+        <v>5900</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>5900</v>
+        <v>377</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>377</v>
+        <v>-1834</v>
       </c>
     </row>
     <row r="13">
@@ -4800,19 +4615,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>160</v>
+        <v>2032</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>2032</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14">
@@ -4822,19 +4637,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>281</v>
+        <v>986</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>986</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15">
@@ -4856,19 +4671,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>760</v>
+        <v>4803</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>4803</v>
+        <v>3595</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3595</v>
+        <v>1101</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>1101</v>
+        <v>998</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>998</v>
+        <v>-10289</v>
       </c>
     </row>
     <row r="17">
@@ -4878,19 +4693,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>-181</v>
+        <v>941</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>941</v>
+        <v>534</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>534</v>
+        <v>-2947</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-2947</v>
+        <v>-488</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>-488</v>
+        <v>-839</v>
       </c>
     </row>
     <row r="18">
@@ -4900,19 +4715,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>940</v>
+        <v>3862</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>3862</v>
+        <v>3061</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3061</v>
+        <v>4049</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>4049</v>
+        <v>1486</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>1486</v>
+        <v>-9450</v>
       </c>
     </row>
     <row r="19">
@@ -4960,7 +4775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4978,19 +4793,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5024,19 +4839,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>151</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -5046,19 +4861,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -5080,19 +4895,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>294</v>
+        <v>229</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>176</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -5102,19 +4917,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>2769</v>
+        <v>3128</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>3128</v>
+        <v>2640</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2640</v>
+        <v>7745</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>7745</v>
+        <v>12703</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>12703</v>
+        <v>9485</v>
       </c>
     </row>
     <row r="9">
@@ -5130,13 +4945,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
+        <v>3436</v>
+      </c>
+      <c r="F9" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>3436</v>
       </c>
     </row>
     <row r="10">
@@ -5146,19 +4961,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>13061</v>
+        <v>7286</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>7286</v>
+        <v>12478</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>12478</v>
+        <v>20879</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>20879</v>
+        <v>26223</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>26223</v>
+        <v>14079</v>
       </c>
     </row>
     <row r="11">
@@ -5168,19 +4983,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>13289</v>
+        <v>7471</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>7471</v>
+        <v>12773</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>12773</v>
+        <v>21108</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>21108</v>
+        <v>26400</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>26400</v>
+        <v>14629</v>
       </c>
     </row>
     <row r="12">
@@ -5190,19 +5005,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>382</v>
+        <v>248</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>116</v>
+        <v>520</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>400</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="13">
@@ -5236,19 +5051,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>382</v>
+        <v>248</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>116</v>
+        <v>520</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>400</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="16">
@@ -5258,15 +5073,17 @@
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
+      <c r="C16" s="16" t="n">
+        <v>1633</v>
+      </c>
       <c r="D16" s="16" t="n">
-        <v>1633</v>
+        <v>14</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>14</v>
+        <v>5063</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>5063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5276,19 +5093,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>459</v>
+        <v>7108</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>7108</v>
+        <v>7386</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>7386</v>
+        <v>9765</v>
       </c>
     </row>
     <row r="18">
@@ -5298,19 +5115,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4245</v>
+        <v>14233</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>14233</v>
+        <v>3262</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3262</v>
+        <v>3373</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>3373</v>
+        <v>8115</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>8115</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="19">
@@ -5320,19 +5137,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>226</v>
+        <v>1113</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1113</v>
+        <v>141</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>141</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
@@ -5342,19 +5159,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>1479</v>
+        <v>534</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0</v>
+        <v>2814</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>2814</v>
+        <v>2778</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>2778</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="21">
@@ -5376,11 +5193,9 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="C22" s="16" t="n">
         <v>4</v>
       </c>
+      <c r="C22" s="16" t="n"/>
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
       <c r="F22" s="16" t="n"/>
@@ -5392,19 +5207,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>5976</v>
+        <v>15893</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>15893</v>
+        <v>18257</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>18257</v>
+        <v>14422</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>14422</v>
+        <v>23482</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>23482</v>
+        <v>24968</v>
       </c>
     </row>
     <row r="24">
@@ -5426,19 +5241,19 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>8934</v>
+        <v>5997</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>5997</v>
+        <v>301</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>224</v>
+        <v>146</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>146</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
@@ -5448,19 +5263,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>15292</v>
+        <v>22139</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>22139</v>
+        <v>18674</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>18674</v>
+        <v>15166</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>15166</v>
+        <v>24028</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>24028</v>
+        <v>27117</v>
       </c>
     </row>
     <row r="27">
@@ -5470,19 +5285,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>28581</v>
+        <v>29609</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>29609</v>
+        <v>31447</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>31447</v>
+        <v>36273</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>36273</v>
+        <v>50428</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>50428</v>
+        <v>41746</v>
       </c>
     </row>
     <row r="28">
@@ -5498,7 +5313,7 @@
         <v>500</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E28" s="16" t="n">
         <v>1000</v>
@@ -5514,19 +5329,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>2651</v>
+        <v>3190</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>3190</v>
+        <v>8381</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>8381</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>8381</v>
+        <v>11068</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>11068</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="30">
@@ -5572,19 +5387,19 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>21151</v>
+        <v>23474</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>23474</v>
+        <v>21344</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>21344</v>
+        <v>11392</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>11392</v>
+        <v>10192</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>10192</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="34">
@@ -5594,19 +5409,19 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>27302</v>
+        <v>28165</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>28165</v>
+        <v>30225</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>30225</v>
+        <v>20774</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>20774</v>
+        <v>22260</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>22260</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="35">
@@ -5616,33 +5431,43 @@
         </is>
       </c>
       <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
+      <c r="C35" s="16" t="n">
+        <v>325</v>
+      </c>
       <c r="D35" s="16" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>250</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>7030</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B37" s="16" t="n"/>
@@ -5654,7 +5479,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B38" s="16" t="n"/>
@@ -5666,91 +5491,97 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>146</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>7030</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>1068</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>366</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>298</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>7650</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>14450</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>28506</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>79</v>
-      </c>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B44" s="16" t="n"/>
@@ -5762,51 +5593,41 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>406</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>1068</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>366</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>298</v>
-      </c>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B46" s="16" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>500</v>
+        <v>163</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>7650</v>
+        <v>13092</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>14450</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B47" s="16" t="n"/>
@@ -5816,127 +5637,69 @@
       <c r="F47" s="16" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>897</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>8219</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>27918</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>28937</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>897</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>15250</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>27918</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>28937</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>725</v>
+        <v>29609</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>373</v>
+        <v>31447</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>99</v>
+        <v>36273</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>163</v>
+        <v>50428</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>13092</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>1133</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>1445</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>897</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>8219</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>27918</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>1279</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>1445</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>897</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>15250</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>27918</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>28581</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>29609</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>31447</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>36273</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>50428</v>
+        <v>41746</v>
       </c>
     </row>
   </sheetData>
@@ -5975,13 +5738,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6416,15 +6179,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_35478205'!$F$54-'balance_raw_35478205'!$F$34</f>
+        <f>'balance_raw_35478205'!$F$50-'balance_raw_35478205'!$F$34</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_35478205'!$E$54-'balance_raw_35478205'!$E$34</f>
+        <f>'balance_raw_35478205'!$E$50-'balance_raw_35478205'!$E$34</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_35478205'!$D$54-'balance_raw_35478205'!$D$34</f>
+        <f>'balance_raw_35478205'!$D$50-'balance_raw_35478205'!$D$34</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6530,15 +6293,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_35478205'!$F$52</f>
+        <f>'balance_raw_35478205'!$F$48</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_35478205'!$E$52</f>
+        <f>'balance_raw_35478205'!$E$48</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_35478205'!$D$52</f>
+        <f>'balance_raw_35478205'!$D$48</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6695,7 +6458,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6813,7 +6576,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6989,7 +6752,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7046,15 +6809,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_35478205'!$F$54="","—",IF(ABS(B25-'balance_raw_35478205'!$F$54)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_35478205'!$F$54,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35478205'!$F$50="","—",IF(ABS(B25-'balance_raw_35478205'!$F$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_35478205'!$F$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_35478205'!$E$54="","—",IF(ABS(C25-'balance_raw_35478205'!$E$54)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_35478205'!$E$54,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35478205'!$E$50="","—",IF(ABS(C25-'balance_raw_35478205'!$E$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_35478205'!$E$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_35478205'!$D$54="","—",IF(ABS(D25-'balance_raw_35478205'!$D$54)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_35478205'!$D$54,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_35478205'!$D$50="","—",IF(ABS(D25-'balance_raw_35478205'!$D$50)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_35478205'!$D$50,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7212,27 +6975,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7258,14 +7021,14 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n"/>
+      <c r="H3" s="35" t="n">
+        <v>170</v>
+      </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
